--- a/data/sources/countries/costa_rica.xlsx
+++ b/data/sources/countries/costa_rica.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI73"/>
+  <dimension ref="A1:BE73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +728,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -835,11 +739,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Anhui Foreign Economic Construction Group</t>
+          <t>Anhui Foreign Economic Construction</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -876,7 +780,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -893,18 +797,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>MONTO Y ANO CORREGIDOS. Estadio Nacional de Costa Rica, donacion del Gobierno de China ejecutada por AFECC. El monto registrado era 146, cifra que no aparece en ninguna fuente y que probablemente provenia de la columna de dolares constantes de AidData; la cifra comprometida es USD 105M. El ano registrado era 2011, que es el de inauguracion; AidData fecha el compromiso en 2009 y la construccion comenzo el 12 de marzo de 2009. NOTA METODOLOGICA: es una donacion, no una inversion ni un contrato comercial.</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>https://observador.cr/constructora-chec-atribuye-encarecimiento-de-obra-en-ruta-32-a-atrasos-en-expropiaciones/</t>
         </is>
@@ -934,7 +830,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1014,25 +910,20 @@
       <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>1</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.recope.go.cr/arbitraje-internacional-resuelve-disolver-liquidar-soresco/</t>
+        </is>
+      </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.nacion.com/el-pais/servicios/laudo-arbitral-disuelve-empresa-ligada-a-fallido/RUGEDCM3UNCI5H2JXBIGGRABAI/story/</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.recope.go.cr/arbitraje-internacional-resuelve-disolver-liquidar-soresco/</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://www.nacion.com/el-pais/servicios/laudo-arbitral-disuelve-empresa-ligada-a-fallido/RUGEDCM3UNCI5H2JXBIGGRABAI/story/</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.lw.com/en/news/latham-victory-costa-rican-refining-company-recope-international-arbitration</t>
         </is>
@@ -1062,7 +953,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1116,6 +1007,11 @@
       <c r="R4" t="n">
         <v>534</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>No</t>
@@ -1129,10 +1025,10 @@
       <c r="BA4" t="n">
         <v>5</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1162,7 +1058,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1216,6 +1112,11 @@
       <c r="R5" t="n">
         <v>534</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>No</t>
@@ -1229,10 +1130,10 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1262,7 +1163,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1316,6 +1217,11 @@
       <c r="R6" t="n">
         <v>534</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>No</t>
@@ -1329,10 +1235,10 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1362,7 +1268,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1416,6 +1322,11 @@
       <c r="R7" t="n">
         <v>534</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>No</t>
@@ -1429,10 +1340,10 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>0</v>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1462,7 +1373,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1516,6 +1427,11 @@
       <c r="R8" t="n">
         <v>534</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>No</t>
@@ -1529,10 +1445,10 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1562,7 +1478,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1616,6 +1532,11 @@
       <c r="R9" t="n">
         <v>534</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>No</t>
@@ -1629,10 +1550,10 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BB9" t="n">
         <v>0</v>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1662,7 +1583,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1716,6 +1637,11 @@
       <c r="R10" t="n">
         <v>534</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>No</t>
@@ -1729,10 +1655,10 @@
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BB10" t="n">
         <v>0</v>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1762,7 +1688,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1816,6 +1742,11 @@
       <c r="R11" t="n">
         <v>534</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1829,10 +1760,10 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BB11" t="n">
         <v>0</v>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1862,7 +1793,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -1916,6 +1847,11 @@
       <c r="R12" t="n">
         <v>534</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>No</t>
@@ -1929,10 +1865,10 @@
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BB12" t="n">
         <v>0</v>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -1962,7 +1898,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2016,6 +1952,11 @@
       <c r="R13" t="n">
         <v>534</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>No</t>
@@ -2029,10 +1970,10 @@
       <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BB13" t="n">
         <v>0</v>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2062,7 +2003,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2116,6 +2057,11 @@
       <c r="R14" t="n">
         <v>534</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>No</t>
@@ -2129,10 +2075,10 @@
       <c r="BA14" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BB14" t="n">
         <v>0</v>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2162,7 +2108,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2216,6 +2162,11 @@
       <c r="R15" t="n">
         <v>534</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>No</t>
@@ -2229,10 +2180,10 @@
       <c r="BA15" t="n">
         <v>5</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BB15" t="n">
         <v>0</v>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2262,7 +2213,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2316,6 +2267,11 @@
       <c r="R16" t="n">
         <v>534</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>No</t>
@@ -2329,10 +2285,10 @@
       <c r="BA16" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BB16" t="n">
         <v>0</v>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2362,7 +2318,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2416,6 +2372,11 @@
       <c r="R17" t="n">
         <v>534</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>No</t>
@@ -2429,10 +2390,10 @@
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BB17" t="n">
         <v>0</v>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2462,7 +2423,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2516,6 +2477,11 @@
       <c r="R18" t="n">
         <v>534</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>No</t>
@@ -2529,10 +2495,10 @@
       <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BB18" t="n">
         <v>0</v>
       </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2562,7 +2528,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2616,6 +2582,11 @@
       <c r="R19" t="n">
         <v>534</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>No</t>
@@ -2629,10 +2600,10 @@
       <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BB19" t="n">
         <v>0</v>
       </c>
-      <c r="BE19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2662,7 +2633,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2716,6 +2687,11 @@
       <c r="R20" t="n">
         <v>534</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>No</t>
@@ -2729,10 +2705,10 @@
       <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BB20" t="n">
         <v>0</v>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2762,7 +2738,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2816,6 +2792,11 @@
       <c r="R21" t="n">
         <v>534</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>No</t>
@@ -2829,10 +2810,10 @@
       <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BB21" t="n">
         <v>0</v>
       </c>
-      <c r="BE21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2862,7 +2843,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -2916,6 +2897,11 @@
       <c r="R22" t="n">
         <v>534</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>No</t>
@@ -2929,10 +2915,10 @@
       <c r="BA22" t="n">
         <v>5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BB22" t="n">
         <v>0</v>
       </c>
-      <c r="BE22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -2962,7 +2948,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3016,6 +3002,11 @@
       <c r="R23" t="n">
         <v>534</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>No</t>
@@ -3029,10 +3020,10 @@
       <c r="BA23" t="n">
         <v>5</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BB23" t="n">
         <v>0</v>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3062,7 +3053,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3116,6 +3107,11 @@
       <c r="R24" t="n">
         <v>534</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>No</t>
@@ -3129,10 +3125,10 @@
       <c r="BA24" t="n">
         <v>5</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BB24" t="n">
         <v>0</v>
       </c>
-      <c r="BE24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3162,7 +3158,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3216,6 +3212,11 @@
       <c r="R25" t="n">
         <v>534</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>No</t>
@@ -3229,10 +3230,10 @@
       <c r="BA25" t="n">
         <v>5</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BB25" t="n">
         <v>0</v>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3262,7 +3263,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3316,6 +3317,11 @@
       <c r="R26" t="n">
         <v>534</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>No</t>
@@ -3329,10 +3335,10 @@
       <c r="BA26" t="n">
         <v>5</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BB26" t="n">
         <v>0</v>
       </c>
-      <c r="BE26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3362,7 +3368,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3416,6 +3422,11 @@
       <c r="R27" t="n">
         <v>534</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>No</t>
@@ -3429,10 +3440,10 @@
       <c r="BA27" t="n">
         <v>5</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BB27" t="n">
         <v>0</v>
       </c>
-      <c r="BE27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3462,7 +3473,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3516,6 +3527,11 @@
       <c r="R28" t="n">
         <v>534</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>No</t>
@@ -3529,10 +3545,10 @@
       <c r="BA28" t="n">
         <v>5</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BB28" t="n">
         <v>0</v>
       </c>
-      <c r="BE28" t="inlineStr">
+      <c r="BC28" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3562,7 +3578,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3616,6 +3632,11 @@
       <c r="R29" t="n">
         <v>534</v>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>No</t>
@@ -3629,10 +3650,10 @@
       <c r="BA29" t="n">
         <v>5</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BB29" t="n">
         <v>0</v>
       </c>
-      <c r="BE29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3662,7 +3683,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3716,6 +3737,11 @@
       <c r="R30" t="n">
         <v>534</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>No</t>
@@ -3729,10 +3755,10 @@
       <c r="BA30" t="n">
         <v>5</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BB30" t="n">
         <v>0</v>
       </c>
-      <c r="BE30" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3762,7 +3788,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3816,6 +3842,11 @@
       <c r="R31" t="n">
         <v>534</v>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>No</t>
@@ -3829,10 +3860,10 @@
       <c r="BA31" t="n">
         <v>5</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BB31" t="n">
         <v>0</v>
       </c>
-      <c r="BE31" t="inlineStr">
+      <c r="BC31" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3862,7 +3893,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -3916,6 +3947,11 @@
       <c r="R32" t="n">
         <v>534</v>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>No</t>
@@ -3929,10 +3965,10 @@
       <c r="BA32" t="n">
         <v>5</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BB32" t="n">
         <v>0</v>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BC32" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -3962,7 +3998,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4016,6 +4052,11 @@
       <c r="R33" t="n">
         <v>534</v>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>No</t>
@@ -4029,10 +4070,10 @@
       <c r="BA33" t="n">
         <v>5</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BB33" t="n">
         <v>0</v>
       </c>
-      <c r="BE33" t="inlineStr">
+      <c r="BC33" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4062,7 +4103,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4116,6 +4157,11 @@
       <c r="R34" t="n">
         <v>534</v>
       </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>No</t>
@@ -4129,10 +4175,10 @@
       <c r="BA34" t="n">
         <v>5</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BB34" t="n">
         <v>0</v>
       </c>
-      <c r="BE34" t="inlineStr">
+      <c r="BC34" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4162,7 +4208,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4216,6 +4262,11 @@
       <c r="R35" t="n">
         <v>534</v>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>No</t>
@@ -4229,10 +4280,10 @@
       <c r="BA35" t="n">
         <v>5</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BB35" t="n">
         <v>0</v>
       </c>
-      <c r="BE35" t="inlineStr">
+      <c r="BC35" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4262,7 +4313,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4316,6 +4367,11 @@
       <c r="R36" t="n">
         <v>534</v>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>No</t>
@@ -4329,10 +4385,10 @@
       <c r="BA36" t="n">
         <v>5</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BB36" t="n">
         <v>0</v>
       </c>
-      <c r="BE36" t="inlineStr">
+      <c r="BC36" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4362,7 +4418,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4416,6 +4472,11 @@
       <c r="R37" t="n">
         <v>534</v>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>No</t>
@@ -4429,10 +4490,10 @@
       <c r="BA37" t="n">
         <v>5</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BB37" t="n">
         <v>0</v>
       </c>
-      <c r="BE37" t="inlineStr">
+      <c r="BC37" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4462,7 +4523,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4516,6 +4577,11 @@
       <c r="R38" t="n">
         <v>534</v>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>No</t>
@@ -4529,10 +4595,10 @@
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BB38" t="n">
         <v>0</v>
       </c>
-      <c r="BE38" t="inlineStr">
+      <c r="BC38" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4562,7 +4628,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4616,6 +4682,11 @@
       <c r="R39" t="n">
         <v>534</v>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>No</t>
@@ -4629,10 +4700,10 @@
       <c r="BA39" t="n">
         <v>5</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BB39" t="n">
         <v>0</v>
       </c>
-      <c r="BE39" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4662,7 +4733,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4716,6 +4787,11 @@
       <c r="R40" t="n">
         <v>534</v>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>No</t>
@@ -4729,10 +4805,10 @@
       <c r="BA40" t="n">
         <v>5</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BB40" t="n">
         <v>0</v>
       </c>
-      <c r="BE40" t="inlineStr">
+      <c r="BC40" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4762,7 +4838,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4816,6 +4892,11 @@
       <c r="R41" t="n">
         <v>534</v>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>No</t>
@@ -4829,10 +4910,10 @@
       <c r="BA41" t="n">
         <v>5</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BB41" t="n">
         <v>0</v>
       </c>
-      <c r="BE41" t="inlineStr">
+      <c r="BC41" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4862,7 +4943,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -4916,6 +4997,11 @@
       <c r="R42" t="n">
         <v>534</v>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>No</t>
@@ -4929,10 +5015,10 @@
       <c r="BA42" t="n">
         <v>5</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BB42" t="n">
         <v>0</v>
       </c>
-      <c r="BE42" t="inlineStr">
+      <c r="BC42" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -4962,7 +5048,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5016,6 +5102,11 @@
       <c r="R43" t="n">
         <v>534</v>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>No</t>
@@ -5029,10 +5120,10 @@
       <c r="BA43" t="n">
         <v>5</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BB43" t="n">
         <v>0</v>
       </c>
-      <c r="BE43" t="inlineStr">
+      <c r="BC43" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5062,7 +5153,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5116,6 +5207,11 @@
       <c r="R44" t="n">
         <v>534</v>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>No</t>
@@ -5129,10 +5225,10 @@
       <c r="BA44" t="n">
         <v>5</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BB44" t="n">
         <v>0</v>
       </c>
-      <c r="BE44" t="inlineStr">
+      <c r="BC44" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5162,7 +5258,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5216,6 +5312,11 @@
       <c r="R45" t="n">
         <v>534</v>
       </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>No</t>
@@ -5229,10 +5330,10 @@
       <c r="BA45" t="n">
         <v>5</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BB45" t="n">
         <v>0</v>
       </c>
-      <c r="BE45" t="inlineStr">
+      <c r="BC45" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5262,7 +5363,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5316,6 +5417,11 @@
       <c r="R46" t="n">
         <v>534</v>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>No</t>
@@ -5329,10 +5435,10 @@
       <c r="BA46" t="n">
         <v>5</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BB46" t="n">
         <v>0</v>
       </c>
-      <c r="BE46" t="inlineStr">
+      <c r="BC46" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5362,7 +5468,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5416,6 +5522,11 @@
       <c r="R47" t="n">
         <v>534</v>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>No</t>
@@ -5429,10 +5540,10 @@
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BB47" t="n">
         <v>0</v>
       </c>
-      <c r="BE47" t="inlineStr">
+      <c r="BC47" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5462,7 +5573,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5516,6 +5627,11 @@
       <c r="R48" t="n">
         <v>534</v>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>No</t>
@@ -5529,10 +5645,10 @@
       <c r="BA48" t="n">
         <v>5</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BB48" t="n">
         <v>0</v>
       </c>
-      <c r="BE48" t="inlineStr">
+      <c r="BC48" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5562,7 +5678,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5616,6 +5732,11 @@
       <c r="R49" t="n">
         <v>534</v>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>No</t>
@@ -5629,10 +5750,10 @@
       <c r="BA49" t="n">
         <v>5</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BB49" t="n">
         <v>0</v>
       </c>
-      <c r="BE49" t="inlineStr">
+      <c r="BC49" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5662,7 +5783,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5716,6 +5837,11 @@
       <c r="R50" t="n">
         <v>534</v>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>No</t>
@@ -5729,10 +5855,10 @@
       <c r="BA50" t="n">
         <v>5</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BB50" t="n">
         <v>0</v>
       </c>
-      <c r="BE50" t="inlineStr">
+      <c r="BC50" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5762,7 +5888,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5816,6 +5942,11 @@
       <c r="R51" t="n">
         <v>534</v>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>No</t>
@@ -5829,10 +5960,10 @@
       <c r="BA51" t="n">
         <v>5</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BB51" t="n">
         <v>0</v>
       </c>
-      <c r="BE51" t="inlineStr">
+      <c r="BC51" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5862,7 +5993,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5916,6 +6047,11 @@
       <c r="R52" t="n">
         <v>534</v>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>No</t>
@@ -5929,10 +6065,10 @@
       <c r="BA52" t="n">
         <v>5</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BB52" t="n">
         <v>0</v>
       </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BC52" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -5962,7 +6098,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6016,6 +6152,11 @@
       <c r="R53" t="n">
         <v>534</v>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>No</t>
@@ -6029,10 +6170,10 @@
       <c r="BA53" t="n">
         <v>5</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BB53" t="n">
         <v>0</v>
       </c>
-      <c r="BE53" t="inlineStr">
+      <c r="BC53" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6062,7 +6203,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6116,6 +6257,11 @@
       <c r="R54" t="n">
         <v>534</v>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>No</t>
@@ -6129,10 +6275,10 @@
       <c r="BA54" t="n">
         <v>5</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BB54" t="n">
         <v>0</v>
       </c>
-      <c r="BE54" t="inlineStr">
+      <c r="BC54" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6162,7 +6308,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6216,6 +6362,11 @@
       <c r="R55" t="n">
         <v>534</v>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>No</t>
@@ -6229,10 +6380,10 @@
       <c r="BA55" t="n">
         <v>5</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BB55" t="n">
         <v>0</v>
       </c>
-      <c r="BE55" t="inlineStr">
+      <c r="BC55" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6262,7 +6413,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6316,6 +6467,11 @@
       <c r="R56" t="n">
         <v>534</v>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>No</t>
@@ -6329,10 +6485,10 @@
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BB56" t="n">
         <v>0</v>
       </c>
-      <c r="BE56" t="inlineStr">
+      <c r="BC56" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6362,7 +6518,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6416,6 +6572,11 @@
       <c r="R57" t="n">
         <v>534</v>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>No</t>
@@ -6429,10 +6590,10 @@
       <c r="BA57" t="n">
         <v>5</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BB57" t="n">
         <v>0</v>
       </c>
-      <c r="BE57" t="inlineStr">
+      <c r="BC57" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6462,7 +6623,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6516,6 +6677,11 @@
       <c r="R58" t="n">
         <v>534</v>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>No</t>
@@ -6529,10 +6695,10 @@
       <c r="BA58" t="n">
         <v>5</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BB58" t="n">
         <v>0</v>
       </c>
-      <c r="BE58" t="inlineStr">
+      <c r="BC58" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6562,7 +6728,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6616,6 +6782,11 @@
       <c r="R59" t="n">
         <v>534</v>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>No</t>
@@ -6629,10 +6800,10 @@
       <c r="BA59" t="n">
         <v>5</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BB59" t="n">
         <v>0</v>
       </c>
-      <c r="BE59" t="inlineStr">
+      <c r="BC59" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6662,7 +6833,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6716,6 +6887,11 @@
       <c r="R60" t="n">
         <v>534</v>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>No</t>
@@ -6729,10 +6905,10 @@
       <c r="BA60" t="n">
         <v>5</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BB60" t="n">
         <v>0</v>
       </c>
-      <c r="BE60" t="inlineStr">
+      <c r="BC60" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6762,7 +6938,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6816,6 +6992,11 @@
       <c r="R61" t="n">
         <v>534</v>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>No</t>
@@ -6829,10 +7010,10 @@
       <c r="BA61" t="n">
         <v>5</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BB61" t="n">
         <v>0</v>
       </c>
-      <c r="BE61" t="inlineStr">
+      <c r="BC61" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6862,7 +7043,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -6916,6 +7097,11 @@
       <c r="R62" t="n">
         <v>534</v>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>No</t>
@@ -6929,10 +7115,10 @@
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BC62" t="n">
+      <c r="BB62" t="n">
         <v>0</v>
       </c>
-      <c r="BE62" t="inlineStr">
+      <c r="BC62" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -6962,7 +7148,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7016,6 +7202,11 @@
       <c r="R63" t="n">
         <v>534</v>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>No</t>
@@ -7029,10 +7220,10 @@
       <c r="BA63" t="n">
         <v>5</v>
       </c>
-      <c r="BC63" t="n">
+      <c r="BB63" t="n">
         <v>0</v>
       </c>
-      <c r="BE63" t="inlineStr">
+      <c r="BC63" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7062,7 +7253,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7116,6 +7307,11 @@
       <c r="R64" t="n">
         <v>534</v>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>No</t>
@@ -7129,10 +7325,10 @@
       <c r="BA64" t="n">
         <v>5</v>
       </c>
-      <c r="BC64" t="n">
+      <c r="BB64" t="n">
         <v>0</v>
       </c>
-      <c r="BE64" t="inlineStr">
+      <c r="BC64" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7162,7 +7358,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7216,6 +7412,11 @@
       <c r="R65" t="n">
         <v>534</v>
       </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>No</t>
@@ -7229,10 +7430,10 @@
       <c r="BA65" t="n">
         <v>5</v>
       </c>
-      <c r="BC65" t="n">
+      <c r="BB65" t="n">
         <v>0</v>
       </c>
-      <c r="BE65" t="inlineStr">
+      <c r="BC65" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7262,7 +7463,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7316,6 +7517,11 @@
       <c r="R66" t="n">
         <v>534</v>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>No</t>
@@ -7329,10 +7535,10 @@
       <c r="BA66" t="n">
         <v>5</v>
       </c>
-      <c r="BC66" t="n">
+      <c r="BB66" t="n">
         <v>0</v>
       </c>
-      <c r="BE66" t="inlineStr">
+      <c r="BC66" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7362,7 +7568,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7416,6 +7622,11 @@
       <c r="R67" t="n">
         <v>534</v>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>No</t>
@@ -7429,10 +7640,10 @@
       <c r="BA67" t="n">
         <v>5</v>
       </c>
-      <c r="BC67" t="n">
+      <c r="BB67" t="n">
         <v>0</v>
       </c>
-      <c r="BE67" t="inlineStr">
+      <c r="BC67" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7462,7 +7673,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7516,6 +7727,11 @@
       <c r="R68" t="n">
         <v>534</v>
       </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>No</t>
@@ -7529,10 +7745,10 @@
       <c r="BA68" t="n">
         <v>5</v>
       </c>
-      <c r="BC68" t="n">
+      <c r="BB68" t="n">
         <v>0</v>
       </c>
-      <c r="BE68" t="inlineStr">
+      <c r="BC68" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7562,7 +7778,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7616,6 +7832,11 @@
       <c r="R69" t="n">
         <v>534</v>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr">
         <is>
           <t>No</t>
@@ -7629,10 +7850,10 @@
       <c r="BA69" t="n">
         <v>5</v>
       </c>
-      <c r="BC69" t="n">
+      <c r="BB69" t="n">
         <v>0</v>
       </c>
-      <c r="BE69" t="inlineStr">
+      <c r="BC69" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7662,7 +7883,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7716,6 +7937,11 @@
       <c r="R70" t="n">
         <v>534</v>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>No</t>
@@ -7729,10 +7955,10 @@
       <c r="BA70" t="n">
         <v>5</v>
       </c>
-      <c r="BC70" t="n">
+      <c r="BB70" t="n">
         <v>0</v>
       </c>
-      <c r="BE70" t="inlineStr">
+      <c r="BC70" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7762,7 +7988,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7816,6 +8042,11 @@
       <c r="R71" t="n">
         <v>534</v>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr">
         <is>
           <t>No</t>
@@ -7829,10 +8060,10 @@
       <c r="BA71" t="n">
         <v>5</v>
       </c>
-      <c r="BC71" t="n">
+      <c r="BB71" t="n">
         <v>0</v>
       </c>
-      <c r="BE71" t="inlineStr">
+      <c r="BC71" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7862,7 +8093,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -7916,6 +8147,11 @@
       <c r="R72" t="n">
         <v>534</v>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr">
         <is>
           <t>No</t>
@@ -7929,10 +8165,10 @@
       <c r="BA72" t="n">
         <v>5</v>
       </c>
-      <c r="BC72" t="n">
+      <c r="BB72" t="n">
         <v>0</v>
       </c>
-      <c r="BE72" t="inlineStr">
+      <c r="BC72" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
@@ -7962,7 +8198,7 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -8016,6 +8252,11 @@
       <c r="R73" t="n">
         <v>534</v>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>No</t>
@@ -8029,10 +8270,10 @@
       <c r="BA73" t="n">
         <v>5</v>
       </c>
-      <c r="BC73" t="n">
+      <c r="BB73" t="n">
         <v>0</v>
       </c>
-      <c r="BE73" t="inlineStr">
+      <c r="BC73" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>

--- a/data/sources/countries/costa_rica.xlsx
+++ b/data/sources/countries/costa_rica.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE73"/>
+  <dimension ref="A1:BG73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,20 +684,30 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -710,6 +719,7 @@
           <t>CRI-0001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -728,10 +738,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G2" t="n">
+        <v>188</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -782,6 +790,9 @@
       <c r="R2" t="n">
         <v>146</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -797,14 +808,53 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="BB2" t="n">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Estadio Nacional de Costa Rica, donacion del Gobierno de China ejecutada por AFECC. El monto registrado era 146, cifra que no aparece en ninguna fuente y que probablemente provenia de la columna de dolares constantes de AidData; la cifra comprometida es USD 105M. El ano registrado era 2011, que es el de inauguracion; AidData fecha el compromiso en 2009 y la construccion comenzo el 12 de marzo de 2009. NOTA METODOLOGICA: es una donacion, no una inversion ni un contrato comercial.</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://observador.cr/constructora-chec-atribuye-encarecimiento-de-obra-en-ruta-32-a-atrasos-en-expropiaciones/</t>
         </is>
       </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -812,6 +862,7 @@
           <t>CRI-0002</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -830,10 +881,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G3" t="n">
+        <v>188</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -889,6 +938,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>50</v>
       </c>
@@ -907,23 +957,57 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>1</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>cancelado</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.recope.go.cr/arbitraje-internacional-resuelve-disolver-liquidar-soresco/</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.nacion.com/el-pais/servicios/laudo-arbitral-disuelve-empresa-ligada-a-fallido/RUGEDCM3UNCI5H2JXBIGGRABAI/story/</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://www.lw.com/en/news/latham-victory-costa-rican-refining-company-recope-international-arbitration</t>
         </is>
@@ -935,6 +1019,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>3</v>
       </c>
@@ -953,10 +1038,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G4" t="n">
+        <v>188</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1007,6 +1090,9 @@
       <c r="R4" t="n">
         <v>534</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1022,17 +1108,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>5</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1040,6 +1158,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>3</v>
       </c>
@@ -1058,10 +1177,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G5" t="n">
+        <v>188</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1112,6 +1229,9 @@
       <c r="R5" t="n">
         <v>534</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1127,17 +1247,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1145,6 +1297,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>3</v>
       </c>
@@ -1163,10 +1316,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G6" t="n">
+        <v>188</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1217,6 +1368,9 @@
       <c r="R6" t="n">
         <v>534</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1232,17 +1386,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1250,6 +1436,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>3</v>
       </c>
@@ -1268,10 +1455,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G7" t="n">
+        <v>188</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1322,6 +1507,9 @@
       <c r="R7" t="n">
         <v>534</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1337,17 +1525,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1355,6 +1575,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>3</v>
       </c>
@@ -1373,10 +1594,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G8" t="n">
+        <v>188</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1427,6 +1646,9 @@
       <c r="R8" t="n">
         <v>534</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1442,17 +1664,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1460,6 +1714,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>3</v>
       </c>
@@ -1478,10 +1733,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G9" t="n">
+        <v>188</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1532,6 +1785,9 @@
       <c r="R9" t="n">
         <v>534</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1547,17 +1803,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
         <v>0</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1565,6 +1853,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>3</v>
       </c>
@@ -1583,10 +1872,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G10" t="n">
+        <v>188</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1637,6 +1924,9 @@
       <c r="R10" t="n">
         <v>534</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1652,17 +1942,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
         <v>0</v>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1670,6 +1992,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>3</v>
       </c>
@@ -1688,10 +2011,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G11" t="n">
+        <v>188</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1742,6 +2063,9 @@
       <c r="R11" t="n">
         <v>534</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1757,17 +2081,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1775,6 +2131,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>3</v>
       </c>
@@ -1793,10 +2150,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G12" t="n">
+        <v>188</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1847,6 +2202,9 @@
       <c r="R12" t="n">
         <v>534</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1862,17 +2220,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
         <v>0</v>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1880,6 +2270,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>3</v>
       </c>
@@ -1898,10 +2289,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G13" t="n">
+        <v>188</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1952,6 +2341,9 @@
       <c r="R13" t="n">
         <v>534</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1967,17 +2359,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1985,6 +2409,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>3</v>
       </c>
@@ -2003,10 +2428,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G14" t="n">
+        <v>188</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2057,6 +2480,9 @@
       <c r="R14" t="n">
         <v>534</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2072,17 +2498,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
         <v>5</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
         <v>0</v>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2090,6 +2548,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>3</v>
       </c>
@@ -2108,10 +2567,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G15" t="n">
+        <v>188</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2162,6 +2619,9 @@
       <c r="R15" t="n">
         <v>534</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2177,17 +2637,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
         <v>5</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
         <v>0</v>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2195,6 +2687,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>3</v>
       </c>
@@ -2213,10 +2706,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G16" t="n">
+        <v>188</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2267,6 +2758,9 @@
       <c r="R16" t="n">
         <v>534</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2282,17 +2776,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
         <v>5</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
         <v>0</v>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2300,6 +2826,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>3</v>
       </c>
@@ -2318,10 +2845,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G17" t="n">
+        <v>188</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2372,6 +2897,9 @@
       <c r="R17" t="n">
         <v>534</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2387,17 +2915,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
         <v>0</v>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2405,6 +2965,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>3</v>
       </c>
@@ -2423,10 +2984,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G18" t="n">
+        <v>188</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2477,6 +3036,9 @@
       <c r="R18" t="n">
         <v>534</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2492,17 +3054,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2510,6 +3104,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>3</v>
       </c>
@@ -2528,10 +3123,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G19" t="n">
+        <v>188</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2582,6 +3175,9 @@
       <c r="R19" t="n">
         <v>534</v>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2597,17 +3193,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2615,6 +3243,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>3</v>
       </c>
@@ -2633,10 +3262,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G20" t="n">
+        <v>188</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2687,6 +3314,9 @@
       <c r="R20" t="n">
         <v>534</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2702,17 +3332,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2720,6 +3382,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>3</v>
       </c>
@@ -2738,10 +3401,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G21" t="n">
+        <v>188</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2792,6 +3453,9 @@
       <c r="R21" t="n">
         <v>534</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2807,17 +3471,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
         <v>0</v>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2825,6 +3521,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>3</v>
       </c>
@@ -2843,10 +3540,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G22" t="n">
+        <v>188</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2897,6 +3592,9 @@
       <c r="R22" t="n">
         <v>534</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2912,17 +3610,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
         <v>5</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2930,6 +3660,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>3</v>
       </c>
@@ -2948,10 +3679,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G23" t="n">
+        <v>188</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3002,6 +3731,9 @@
       <c r="R23" t="n">
         <v>534</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3017,17 +3749,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
         <v>5</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3035,6 +3799,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>3</v>
       </c>
@@ -3053,10 +3818,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G24" t="n">
+        <v>188</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3107,6 +3870,9 @@
       <c r="R24" t="n">
         <v>534</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3122,17 +3888,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
         <v>5</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="n">
         <v>0</v>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3140,6 +3938,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>3</v>
       </c>
@@ -3158,10 +3957,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G25" t="n">
+        <v>188</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3212,6 +4009,9 @@
       <c r="R25" t="n">
         <v>534</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3227,17 +4027,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
         <v>5</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3245,6 +4077,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>3</v>
       </c>
@@ -3263,10 +4096,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G26" t="n">
+        <v>188</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3317,6 +4148,9 @@
       <c r="R26" t="n">
         <v>534</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3332,17 +4166,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
         <v>5</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="n">
         <v>0</v>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3350,6 +4216,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>3</v>
       </c>
@@ -3368,10 +4235,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G27" t="n">
+        <v>188</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3422,6 +4287,9 @@
       <c r="R27" t="n">
         <v>534</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3437,17 +4305,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
         <v>5</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
         <v>0</v>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3455,6 +4355,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>3</v>
       </c>
@@ -3473,10 +4374,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G28" t="n">
+        <v>188</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3527,6 +4426,9 @@
       <c r="R28" t="n">
         <v>534</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3542,17 +4444,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
         <v>5</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
         <v>0</v>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3560,6 +4494,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>3</v>
       </c>
@@ -3578,10 +4513,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G29" t="n">
+        <v>188</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3632,6 +4565,9 @@
       <c r="R29" t="n">
         <v>534</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3647,17 +4583,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3665,6 +4633,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>3</v>
       </c>
@@ -3683,10 +4652,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G30" t="n">
+        <v>188</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3737,6 +4704,9 @@
       <c r="R30" t="n">
         <v>534</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3752,17 +4722,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
         <v>5</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="n">
         <v>0</v>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3770,6 +4772,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>3</v>
       </c>
@@ -3788,10 +4791,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G31" t="n">
+        <v>188</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3842,6 +4843,9 @@
       <c r="R31" t="n">
         <v>534</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3857,17 +4861,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
         <v>5</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="n">
         <v>0</v>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3875,6 +4911,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>3</v>
       </c>
@@ -3893,10 +4930,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G32" t="n">
+        <v>188</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3947,6 +4982,9 @@
       <c r="R32" t="n">
         <v>534</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3962,17 +5000,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
         <v>5</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3980,6 +5050,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>3</v>
       </c>
@@ -3998,10 +5069,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G33" t="n">
+        <v>188</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4052,6 +5121,9 @@
       <c r="R33" t="n">
         <v>534</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4067,17 +5139,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
         <v>5</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="n">
         <v>0</v>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4085,6 +5189,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>3</v>
       </c>
@@ -4103,10 +5208,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G34" t="n">
+        <v>188</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4157,6 +5260,9 @@
       <c r="R34" t="n">
         <v>534</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4172,17 +5278,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>5</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="n">
         <v>0</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4190,6 +5328,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>3</v>
       </c>
@@ -4208,10 +5347,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G35" t="n">
+        <v>188</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4262,6 +5399,9 @@
       <c r="R35" t="n">
         <v>534</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4277,17 +5417,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>5</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4295,6 +5467,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>3</v>
       </c>
@@ -4313,10 +5486,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G36" t="n">
+        <v>188</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4367,6 +5538,9 @@
       <c r="R36" t="n">
         <v>534</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4382,17 +5556,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>5</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="n">
         <v>0</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4400,6 +5606,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>3</v>
       </c>
@@ -4418,10 +5625,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G37" t="n">
+        <v>188</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4472,6 +5677,9 @@
       <c r="R37" t="n">
         <v>534</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4487,17 +5695,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>5</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4505,6 +5745,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>3</v>
       </c>
@@ -4523,10 +5764,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G38" t="n">
+        <v>188</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4577,6 +5816,9 @@
       <c r="R38" t="n">
         <v>534</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4592,17 +5834,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>5</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4610,6 +5884,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>3</v>
       </c>
@@ -4628,10 +5903,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G39" t="n">
+        <v>188</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4682,6 +5955,9 @@
       <c r="R39" t="n">
         <v>534</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4697,17 +5973,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>5</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4715,6 +6023,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>3</v>
       </c>
@@ -4733,10 +6042,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G40" t="n">
+        <v>188</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4787,6 +6094,9 @@
       <c r="R40" t="n">
         <v>534</v>
       </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4802,17 +6112,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>5</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
         <v>0</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4820,6 +6162,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>3</v>
       </c>
@@ -4838,10 +6181,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G41" t="n">
+        <v>188</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4892,6 +6233,9 @@
       <c r="R41" t="n">
         <v>534</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4907,17 +6251,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>5</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="n">
         <v>0</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4925,6 +6301,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>3</v>
       </c>
@@ -4943,10 +6320,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G42" t="n">
+        <v>188</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4997,6 +6372,9 @@
       <c r="R42" t="n">
         <v>534</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5012,17 +6390,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>5</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="n">
         <v>0</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5030,6 +6440,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>3</v>
       </c>
@@ -5048,10 +6459,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G43" t="n">
+        <v>188</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5102,6 +6511,9 @@
       <c r="R43" t="n">
         <v>534</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5117,17 +6529,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>5</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="n">
         <v>0</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5135,6 +6579,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>3</v>
       </c>
@@ -5153,10 +6598,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G44" t="n">
+        <v>188</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5207,6 +6650,9 @@
       <c r="R44" t="n">
         <v>534</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5222,17 +6668,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>5</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="n">
         <v>0</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5240,6 +6718,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>3</v>
       </c>
@@ -5258,10 +6737,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G45" t="n">
+        <v>188</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5312,6 +6789,9 @@
       <c r="R45" t="n">
         <v>534</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5327,17 +6807,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>5</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="n">
         <v>0</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5345,6 +6857,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>3</v>
       </c>
@@ -5363,10 +6876,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G46" t="n">
+        <v>188</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5417,6 +6928,9 @@
       <c r="R46" t="n">
         <v>534</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5432,17 +6946,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>5</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="n">
         <v>0</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5450,6 +6996,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>3</v>
       </c>
@@ -5468,10 +7015,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G47" t="n">
+        <v>188</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5522,6 +7067,9 @@
       <c r="R47" t="n">
         <v>534</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5537,17 +7085,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>5</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
         <v>0</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5555,6 +7135,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>3</v>
       </c>
@@ -5573,10 +7154,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G48" t="n">
+        <v>188</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5627,6 +7206,9 @@
       <c r="R48" t="n">
         <v>534</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5642,17 +7224,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>5</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
         <v>0</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5660,6 +7274,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>3</v>
       </c>
@@ -5678,10 +7293,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G49" t="n">
+        <v>188</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5732,6 +7345,9 @@
       <c r="R49" t="n">
         <v>534</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5747,17 +7363,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>5</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="n">
         <v>0</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5765,6 +7413,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>3</v>
       </c>
@@ -5783,10 +7432,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G50" t="n">
+        <v>188</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5837,6 +7484,9 @@
       <c r="R50" t="n">
         <v>534</v>
       </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5852,17 +7502,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>5</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
         <v>0</v>
       </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5870,6 +7552,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>3</v>
       </c>
@@ -5888,10 +7571,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G51" t="n">
+        <v>188</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5942,6 +7623,9 @@
       <c r="R51" t="n">
         <v>534</v>
       </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5957,17 +7641,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>5</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
         <v>0</v>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5975,6 +7691,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>3</v>
       </c>
@@ -5993,10 +7710,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G52" t="n">
+        <v>188</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -6047,6 +7762,9 @@
       <c r="R52" t="n">
         <v>534</v>
       </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6062,17 +7780,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>5</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="n">
         <v>0</v>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6080,6 +7830,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>3</v>
       </c>
@@ -6098,10 +7849,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G53" t="n">
+        <v>188</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6152,6 +7901,9 @@
       <c r="R53" t="n">
         <v>534</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6167,17 +7919,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>5</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="n">
         <v>0</v>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6185,6 +7969,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>3</v>
       </c>
@@ -6203,10 +7988,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G54" t="n">
+        <v>188</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6257,6 +8040,9 @@
       <c r="R54" t="n">
         <v>534</v>
       </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6272,17 +8058,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
         <v>5</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="n">
         <v>0</v>
       </c>
-      <c r="BC54" t="inlineStr">
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6290,6 +8108,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>3</v>
       </c>
@@ -6308,10 +8127,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G55" t="n">
+        <v>188</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6362,6 +8179,9 @@
       <c r="R55" t="n">
         <v>534</v>
       </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6377,17 +8197,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
         <v>5</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="n">
         <v>0</v>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6395,6 +8247,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>3</v>
       </c>
@@ -6413,10 +8266,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G56" t="n">
+        <v>188</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -6467,6 +8318,9 @@
       <c r="R56" t="n">
         <v>534</v>
       </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6482,17 +8336,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
         <v>5</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="n">
         <v>0</v>
       </c>
-      <c r="BC56" t="inlineStr">
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6500,6 +8386,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>3</v>
       </c>
@@ -6518,10 +8405,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G57" t="n">
+        <v>188</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -6572,6 +8457,9 @@
       <c r="R57" t="n">
         <v>534</v>
       </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6587,17 +8475,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
         <v>5</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="n">
         <v>0</v>
       </c>
-      <c r="BC57" t="inlineStr">
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6605,6 +8525,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>3</v>
       </c>
@@ -6623,10 +8544,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G58" t="n">
+        <v>188</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -6677,6 +8596,9 @@
       <c r="R58" t="n">
         <v>534</v>
       </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6692,17 +8614,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
         <v>5</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="n">
         <v>0</v>
       </c>
-      <c r="BC58" t="inlineStr">
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6710,6 +8664,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>3</v>
       </c>
@@ -6728,10 +8683,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G59" t="n">
+        <v>188</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -6782,6 +8735,9 @@
       <c r="R59" t="n">
         <v>534</v>
       </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6797,17 +8753,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
         <v>5</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="n">
         <v>0</v>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6815,6 +8803,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>3</v>
       </c>
@@ -6833,10 +8822,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G60" t="n">
+        <v>188</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -6887,6 +8874,9 @@
       <c r="R60" t="n">
         <v>534</v>
       </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6902,17 +8892,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
         <v>5</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="n">
         <v>0</v>
       </c>
-      <c r="BC60" t="inlineStr">
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6920,6 +8942,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>3</v>
       </c>
@@ -6938,10 +8961,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G61" t="n">
+        <v>188</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -6992,6 +9013,9 @@
       <c r="R61" t="n">
         <v>534</v>
       </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7007,17 +9031,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
         <v>5</v>
       </c>
-      <c r="BB61" t="n">
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>0</v>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7025,6 +9081,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>3</v>
       </c>
@@ -7043,10 +9100,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G62" t="n">
+        <v>188</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7097,6 +9152,9 @@
       <c r="R62" t="n">
         <v>534</v>
       </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7112,17 +9170,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BB62" t="n">
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="n">
         <v>0</v>
       </c>
-      <c r="BC62" t="inlineStr">
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7130,6 +9220,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>3</v>
       </c>
@@ -7148,10 +9239,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G63" t="n">
+        <v>188</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -7202,6 +9291,9 @@
       <c r="R63" t="n">
         <v>534</v>
       </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7217,17 +9309,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
         <v>5</v>
       </c>
-      <c r="BB63" t="n">
+      <c r="BB63" t="inlineStr"/>
+      <c r="BC63" t="n">
         <v>0</v>
       </c>
-      <c r="BC63" t="inlineStr">
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7235,6 +9359,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>3</v>
       </c>
@@ -7253,10 +9378,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G64" t="n">
+        <v>188</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -7307,6 +9430,9 @@
       <c r="R64" t="n">
         <v>534</v>
       </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7322,17 +9448,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
         <v>5</v>
       </c>
-      <c r="BB64" t="n">
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="n">
         <v>0</v>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7340,6 +9498,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>3</v>
       </c>
@@ -7358,10 +9517,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G65" t="n">
+        <v>188</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7412,6 +9569,9 @@
       <c r="R65" t="n">
         <v>534</v>
       </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7427,17 +9587,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
         <v>5</v>
       </c>
-      <c r="BB65" t="n">
+      <c r="BB65" t="inlineStr"/>
+      <c r="BC65" t="n">
         <v>0</v>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7445,6 +9637,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>3</v>
       </c>
@@ -7463,10 +9656,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G66" t="n">
+        <v>188</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -7517,6 +9708,9 @@
       <c r="R66" t="n">
         <v>534</v>
       </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7532,17 +9726,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
       <c r="BA66" t="n">
         <v>5</v>
       </c>
-      <c r="BB66" t="n">
+      <c r="BB66" t="inlineStr"/>
+      <c r="BC66" t="n">
         <v>0</v>
       </c>
-      <c r="BC66" t="inlineStr">
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7550,6 +9776,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>3</v>
       </c>
@@ -7568,10 +9795,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G67" t="n">
+        <v>188</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -7622,6 +9847,9 @@
       <c r="R67" t="n">
         <v>534</v>
       </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7637,17 +9865,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
       <c r="BA67" t="n">
         <v>5</v>
       </c>
-      <c r="BB67" t="n">
+      <c r="BB67" t="inlineStr"/>
+      <c r="BC67" t="n">
         <v>0</v>
       </c>
-      <c r="BC67" t="inlineStr">
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7655,6 +9915,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>3</v>
       </c>
@@ -7673,10 +9934,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G68" t="n">
+        <v>188</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7727,6 +9986,9 @@
       <c r="R68" t="n">
         <v>534</v>
       </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7742,17 +10004,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
         <v>5</v>
       </c>
-      <c r="BB68" t="n">
+      <c r="BB68" t="inlineStr"/>
+      <c r="BC68" t="n">
         <v>0</v>
       </c>
-      <c r="BC68" t="inlineStr">
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7760,6 +10054,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>3</v>
       </c>
@@ -7778,10 +10073,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G69" t="n">
+        <v>188</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7832,6 +10125,9 @@
       <c r="R69" t="n">
         <v>534</v>
       </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7847,17 +10143,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
         <v>5</v>
       </c>
-      <c r="BB69" t="n">
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="n">
         <v>0</v>
       </c>
-      <c r="BC69" t="inlineStr">
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7865,6 +10193,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>3</v>
       </c>
@@ -7883,10 +10212,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G70" t="n">
+        <v>188</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7937,6 +10264,9 @@
       <c r="R70" t="n">
         <v>534</v>
       </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7952,17 +10282,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
         <v>5</v>
       </c>
-      <c r="BB70" t="n">
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="n">
         <v>0</v>
       </c>
-      <c r="BC70" t="inlineStr">
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7970,6 +10332,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>3</v>
       </c>
@@ -7988,10 +10351,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G71" t="n">
+        <v>188</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -8042,6 +10403,9 @@
       <c r="R71" t="n">
         <v>534</v>
       </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8057,17 +10421,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
         <v>5</v>
       </c>
-      <c r="BB71" t="n">
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="n">
         <v>0</v>
       </c>
-      <c r="BC71" t="inlineStr">
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8075,6 +10471,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>3</v>
       </c>
@@ -8093,10 +10490,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G72" t="n">
+        <v>188</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -8147,6 +10542,9 @@
       <c r="R72" t="n">
         <v>534</v>
       </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8162,17 +10560,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
         <v>5</v>
       </c>
-      <c r="BB72" t="n">
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="n">
         <v>0</v>
       </c>
-      <c r="BC72" t="inlineStr">
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8180,6 +10610,7 @@
           <t>CRI-0003</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>3</v>
       </c>
@@ -8198,10 +10629,8 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="G73" t="n">
+        <v>188</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -8252,6 +10681,9 @@
       <c r="R73" t="n">
         <v>534</v>
       </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8267,17 +10699,49 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
         <v>5</v>
       </c>
-      <c r="BB73" t="n">
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="n">
         <v>0</v>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr">
         <is>
           <t>https://www.crhoy.com/nacionales/el-fin-de-la-refineria-china-soresco-paso-anos-devorando-millones-sin-hacer-nada/</t>
         </is>
       </c>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
